--- a/completed/coupling_10.1039.d4mr00031e.xlsx
+++ b/completed/coupling_10.1039.d4mr00031e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/completed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C7A1AD-5AD1-AC4D-B922-72BBC472D491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25EF210-125A-2042-98AD-98E32919B174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="24260" windowHeight="20500" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="50">
   <si>
     <t>REACTION</t>
   </si>
@@ -246,19 +246,10 @@
     </r>
   </si>
   <si>
-    <t>liquid_assisted</t>
-  </si>
-  <si>
     <t>ball_material</t>
   </si>
   <si>
     <t>cell_material</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Stainless Steel</t>
@@ -891,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C7A012-DC9A-214C-8A2F-E48641012DAD}">
-  <dimension ref="A2:X65"/>
+  <dimension ref="A2:W65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -903,12 +894,12 @@
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
       <c r="B3" s="12" t="s">
         <v>3</v>
@@ -926,22 +917,22 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="13" t="s">
         <v>22</v>
@@ -959,10 +950,10 @@
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -972,14 +963,13 @@
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -1011,12 +1001,11 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="4"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="4"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R7" s="4"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="5" t="s">
         <v>9</v>
@@ -1066,16 +1055,13 @@
       <c r="Q8" t="s">
         <v>41</v>
       </c>
-      <c r="R8" t="s">
-        <v>42</v>
-      </c>
-      <c r="S8" s="6" t="s">
+      <c r="R8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="W8" s="5"/>
-      <c r="X8" s="6"/>
-    </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V8" s="5"/>
+      <c r="W8" s="6"/>
+    </row>
+    <row r="9" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
@@ -1095,12 +1081,11 @@
       <c r="O9"/>
       <c r="P9"/>
       <c r="Q9"/>
-      <c r="R9"/>
-      <c r="S9" s="11"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="11"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R9" s="11"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="11"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>27</v>
@@ -1145,20 +1130,17 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="s">
-        <v>45</v>
-      </c>
-      <c r="R10" t="s">
-        <v>45</v>
-      </c>
-      <c r="S10" s="6">
+        <v>42</v>
+      </c>
+      <c r="R10" s="6">
         <f>2*60*60</f>
         <v>7200</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>27</v>
@@ -1199,20 +1181,17 @@
         <v>30</v>
       </c>
       <c r="P11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="s">
-        <v>45</v>
-      </c>
-      <c r="R11" t="s">
-        <v>45</v>
-      </c>
-      <c r="S11" s="6">
+        <v>42</v>
+      </c>
+      <c r="R11" s="6">
         <f>2*60*60</f>
         <v>7200</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>27</v>
@@ -1257,20 +1236,17 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="s">
-        <v>45</v>
-      </c>
-      <c r="R12" t="s">
-        <v>45</v>
-      </c>
-      <c r="S12" s="6">
+        <v>42</v>
+      </c>
+      <c r="R12" s="6">
         <f>2*60*60</f>
         <v>7200</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>27</v>
@@ -1311,20 +1287,17 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="s">
-        <v>45</v>
-      </c>
-      <c r="R13" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="6">
+        <v>42</v>
+      </c>
+      <c r="R13" s="6">
         <f>2*60*60</f>
         <v>7200</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="19" t="s">
         <v>27</v>
@@ -1369,19 +1342,16 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q14" t="s">
-        <v>45</v>
-      </c>
-      <c r="R14" t="s">
-        <v>45</v>
-      </c>
-      <c r="S14" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R14" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="19" t="s">
         <v>27</v>
@@ -1422,19 +1392,16 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="s">
-        <v>45</v>
-      </c>
-      <c r="R15" t="s">
-        <v>45</v>
-      </c>
-      <c r="S15" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="18" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="R15" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="19" t="s">
         <v>27</v>
@@ -1479,19 +1446,16 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q16" t="s">
-        <v>45</v>
-      </c>
-      <c r="R16" t="s">
-        <v>45</v>
-      </c>
-      <c r="S16" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="18" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="R16" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="19" t="s">
         <v>27</v>
@@ -1532,19 +1496,16 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="s">
-        <v>45</v>
-      </c>
-      <c r="R17" t="s">
-        <v>45</v>
-      </c>
-      <c r="S17" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R17" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="19" t="s">
         <v>27</v>
@@ -1589,19 +1550,16 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="s">
-        <v>45</v>
-      </c>
-      <c r="R18" t="s">
-        <v>45</v>
-      </c>
-      <c r="S18" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R18" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="19" t="s">
         <v>27</v>
@@ -1642,19 +1600,16 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q19" t="s">
-        <v>45</v>
-      </c>
-      <c r="R19" t="s">
-        <v>45</v>
-      </c>
-      <c r="S19" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R19" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
       <c r="B20" s="19" t="s">
         <v>27</v>
@@ -1699,19 +1654,16 @@
         <v>30</v>
       </c>
       <c r="P20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q20" t="s">
-        <v>45</v>
-      </c>
-      <c r="R20" t="s">
-        <v>45</v>
-      </c>
-      <c r="S20" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R20" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="19" t="s">
         <v>27</v>
@@ -1752,19 +1704,16 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q21" t="s">
-        <v>45</v>
-      </c>
-      <c r="R21" t="s">
-        <v>45</v>
-      </c>
-      <c r="S21" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R21" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="15"/>
       <c r="B22" s="19" t="s">
         <v>27</v>
@@ -1809,19 +1758,16 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="s">
-        <v>45</v>
-      </c>
-      <c r="R22" t="s">
-        <v>45</v>
-      </c>
-      <c r="S22" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R22" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" s="19" t="s">
         <v>27</v>
@@ -1862,19 +1808,16 @@
         <v>30</v>
       </c>
       <c r="P23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q23" t="s">
-        <v>45</v>
-      </c>
-      <c r="R23" t="s">
-        <v>45</v>
-      </c>
-      <c r="S23" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R23" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
       <c r="B24" s="19" t="s">
         <v>27</v>
@@ -1919,19 +1862,16 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q24" t="s">
-        <v>45</v>
-      </c>
-      <c r="R24" t="s">
-        <v>45</v>
-      </c>
-      <c r="S24" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R24" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" s="19" t="s">
         <v>27</v>
@@ -1972,19 +1912,16 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="s">
-        <v>45</v>
-      </c>
-      <c r="R25" t="s">
-        <v>45</v>
-      </c>
-      <c r="S25" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R25" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
       <c r="B26" s="19" t="s">
         <v>27</v>
@@ -2032,16 +1969,13 @@
         <v>43</v>
       </c>
       <c r="Q26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R26" t="s">
-        <v>45</v>
-      </c>
-      <c r="S26" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R26" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" s="19" t="s">
         <v>27</v>
@@ -2082,19 +2016,16 @@
         <v>30</v>
       </c>
       <c r="P27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q27" t="s">
-        <v>46</v>
-      </c>
-      <c r="R27" t="s">
-        <v>45</v>
-      </c>
-      <c r="S27" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R27" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="19" t="s">
         <v>27</v>
@@ -2139,19 +2070,16 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" t="s">
         <v>43</v>
       </c>
-      <c r="Q28" t="s">
-        <v>45</v>
-      </c>
-      <c r="R28" t="s">
-        <v>46</v>
-      </c>
-      <c r="S28" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R28" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" s="19" t="s">
         <v>27</v>
@@ -2192,19 +2120,16 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q29" t="s">
-        <v>45</v>
-      </c>
-      <c r="R29" t="s">
-        <v>46</v>
-      </c>
-      <c r="S29" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="R29" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" s="19" t="s">
         <v>27</v>
@@ -2252,16 +2177,13 @@
         <v>43</v>
       </c>
       <c r="Q30" t="s">
-        <v>46</v>
-      </c>
-      <c r="R30" t="s">
-        <v>46</v>
-      </c>
-      <c r="S30" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="R30" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" s="19" t="s">
         <v>27</v>
@@ -2302,19 +2224,16 @@
         <v>30</v>
       </c>
       <c r="P31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q31" t="s">
-        <v>46</v>
-      </c>
-      <c r="R31" t="s">
-        <v>46</v>
-      </c>
-      <c r="S31" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="R31" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
       <c r="B32" s="19" t="s">
         <v>27</v>
@@ -2362,16 +2281,13 @@
         <v>43</v>
       </c>
       <c r="Q32" t="s">
-        <v>46</v>
-      </c>
-      <c r="R32" t="s">
-        <v>47</v>
-      </c>
-      <c r="S32" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="R32" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="15"/>
       <c r="B33" s="19" t="s">
         <v>27</v>
@@ -2412,19 +2328,16 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" t="s">
         <v>44</v>
       </c>
-      <c r="Q33" t="s">
-        <v>46</v>
-      </c>
-      <c r="R33" t="s">
-        <v>47</v>
-      </c>
-      <c r="S33" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R33" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
       <c r="B34" s="19" t="s">
         <v>27</v>
@@ -2472,16 +2385,13 @@
         <v>43</v>
       </c>
       <c r="Q34" t="s">
-        <v>46</v>
-      </c>
-      <c r="R34" t="s">
-        <v>45</v>
-      </c>
-      <c r="S34" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R34" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="15"/>
       <c r="B35" s="19" t="s">
         <v>27</v>
@@ -2522,19 +2432,16 @@
         <v>30</v>
       </c>
       <c r="P35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q35" t="s">
-        <v>46</v>
-      </c>
-      <c r="R35" t="s">
-        <v>45</v>
-      </c>
-      <c r="S35" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R35" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
       <c r="B36" s="19" t="s">
         <v>27</v>
@@ -2579,19 +2486,16 @@
         <v>30</v>
       </c>
       <c r="P36" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q36" t="s">
         <v>43</v>
       </c>
-      <c r="Q36" t="s">
-        <v>45</v>
-      </c>
-      <c r="R36" t="s">
-        <v>46</v>
-      </c>
-      <c r="S36" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R36" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
       <c r="B37" s="19" t="s">
         <v>27</v>
@@ -2632,19 +2536,16 @@
         <v>30</v>
       </c>
       <c r="P37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q37" t="s">
-        <v>45</v>
-      </c>
-      <c r="R37" t="s">
-        <v>46</v>
-      </c>
-      <c r="S37" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="R37" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="15"/>
       <c r="B38" s="19" t="s">
         <v>27</v>
@@ -2692,16 +2593,13 @@
         <v>43</v>
       </c>
       <c r="Q38" t="s">
-        <v>46</v>
-      </c>
-      <c r="R38" t="s">
-        <v>46</v>
-      </c>
-      <c r="S38" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="R38" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="15"/>
       <c r="B39" s="19" t="s">
         <v>27</v>
@@ -2742,19 +2640,16 @@
         <v>30</v>
       </c>
       <c r="P39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q39" t="s">
-        <v>46</v>
-      </c>
-      <c r="R39" t="s">
-        <v>46</v>
-      </c>
-      <c r="S39" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="R39" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="15"/>
       <c r="B40" s="19" t="s">
         <v>27</v>
@@ -2802,16 +2697,13 @@
         <v>43</v>
       </c>
       <c r="Q40" t="s">
-        <v>46</v>
-      </c>
-      <c r="R40" t="s">
-        <v>47</v>
-      </c>
-      <c r="S40" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="R40" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="15"/>
       <c r="B41" s="19" t="s">
         <v>27</v>
@@ -2852,19 +2744,16 @@
         <v>30</v>
       </c>
       <c r="P41" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q41" t="s">
         <v>44</v>
       </c>
-      <c r="Q41" t="s">
-        <v>46</v>
-      </c>
-      <c r="R41" t="s">
-        <v>47</v>
-      </c>
-      <c r="S41" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R41" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="15"/>
       <c r="B42" s="19" t="s">
         <v>27</v>
@@ -2906,19 +2795,16 @@
         <v>30</v>
       </c>
       <c r="P42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q42" t="s">
-        <v>45</v>
-      </c>
-      <c r="R42" t="s">
-        <v>45</v>
-      </c>
-      <c r="S42" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R42" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" s="19" t="s">
         <v>27</v>
@@ -2960,19 +2846,16 @@
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q43" t="s">
-        <v>45</v>
-      </c>
-      <c r="R43" t="s">
-        <v>45</v>
-      </c>
-      <c r="S43" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R43" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" s="19" t="s">
         <v>27</v>
@@ -3014,19 +2897,16 @@
         <v>30</v>
       </c>
       <c r="P44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q44" t="s">
-        <v>45</v>
-      </c>
-      <c r="R44" t="s">
-        <v>45</v>
-      </c>
-      <c r="S44" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R44" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="15"/>
       <c r="B45" s="19" t="s">
         <v>27</v>
@@ -3068,19 +2948,16 @@
         <v>30</v>
       </c>
       <c r="P45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q45" t="s">
-        <v>45</v>
-      </c>
-      <c r="R45" t="s">
-        <v>45</v>
-      </c>
-      <c r="S45" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R45" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="15"/>
       <c r="B46" s="19" t="s">
         <v>27</v>
@@ -3126,19 +3003,16 @@
         <v>30</v>
       </c>
       <c r="P46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q46" t="s">
-        <v>45</v>
-      </c>
-      <c r="R46" t="s">
-        <v>45</v>
-      </c>
-      <c r="S46" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R46" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="15"/>
       <c r="B47" s="19" t="s">
         <v>27</v>
@@ -3184,19 +3058,16 @@
         <v>30</v>
       </c>
       <c r="P47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q47" t="s">
-        <v>45</v>
-      </c>
-      <c r="R47" t="s">
-        <v>45</v>
-      </c>
-      <c r="S47" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R47" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
       <c r="B48" s="19" t="s">
         <v>27</v>
@@ -3242,19 +3113,16 @@
         <v>30</v>
       </c>
       <c r="P48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q48" t="s">
-        <v>45</v>
-      </c>
-      <c r="R48" t="s">
-        <v>45</v>
-      </c>
-      <c r="S48" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R48" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
       <c r="B49" s="19" t="s">
         <v>27</v>
@@ -3300,19 +3168,16 @@
         <v>30</v>
       </c>
       <c r="P49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q49" t="s">
-        <v>45</v>
-      </c>
-      <c r="R49" t="s">
-        <v>45</v>
-      </c>
-      <c r="S49" s="20">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="R49" s="20">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="15"/>
       <c r="B50" s="5"/>
       <c r="C50" s="6"/>
@@ -3327,9 +3192,8 @@
       <c r="L50" s="5"/>
       <c r="M50" s="6"/>
       <c r="N50" s="5"/>
-      <c r="P50" s="6"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" s="5"/>
       <c r="C51" s="6"/>
@@ -3344,9 +3208,8 @@
       <c r="L51" s="5"/>
       <c r="M51" s="6"/>
       <c r="N51" s="5"/>
-      <c r="P51" s="6"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="15"/>
       <c r="B52" s="5"/>
       <c r="C52" s="6"/>
@@ -3361,9 +3224,8 @@
       <c r="L52" s="5"/>
       <c r="M52" s="6"/>
       <c r="N52" s="5"/>
-      <c r="P52" s="6"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="15"/>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
@@ -3378,9 +3240,8 @@
       <c r="L53" s="5"/>
       <c r="M53" s="6"/>
       <c r="N53" s="5"/>
-      <c r="P53" s="6"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="15"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -3395,9 +3256,8 @@
       <c r="L54" s="5"/>
       <c r="M54" s="6"/>
       <c r="N54" s="5"/>
-      <c r="P54" s="6"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="15"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -3412,9 +3272,8 @@
       <c r="L55" s="5"/>
       <c r="M55" s="6"/>
       <c r="N55" s="5"/>
-      <c r="P55" s="6"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="15"/>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -3429,9 +3288,8 @@
       <c r="L56" s="5"/>
       <c r="M56" s="6"/>
       <c r="N56" s="5"/>
-      <c r="P56" s="6"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="15"/>
       <c r="B57" s="5"/>
       <c r="C57" s="6"/>
@@ -3446,9 +3304,8 @@
       <c r="L57" s="5"/>
       <c r="M57" s="6"/>
       <c r="N57" s="5"/>
-      <c r="P57" s="6"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="15"/>
       <c r="B58" s="5"/>
       <c r="C58" s="6"/>
@@ -3463,9 +3320,8 @@
       <c r="L58" s="5"/>
       <c r="M58" s="6"/>
       <c r="N58" s="5"/>
-      <c r="P58" s="6"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="15"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -3480,9 +3336,8 @@
       <c r="L59" s="5"/>
       <c r="M59" s="6"/>
       <c r="N59" s="5"/>
-      <c r="P59" s="6"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="15"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -3497,9 +3352,8 @@
       <c r="L60" s="5"/>
       <c r="M60" s="6"/>
       <c r="N60" s="5"/>
-      <c r="P60" s="6"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="15"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -3514,9 +3368,8 @@
       <c r="L61" s="5"/>
       <c r="M61" s="6"/>
       <c r="N61" s="5"/>
-      <c r="P61" s="6"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="15"/>
       <c r="B62" s="5"/>
       <c r="C62" s="6"/>
@@ -3531,9 +3384,8 @@
       <c r="L62" s="5"/>
       <c r="M62" s="6"/>
       <c r="N62" s="5"/>
-      <c r="P62" s="6"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="15"/>
       <c r="B63" s="5"/>
       <c r="C63" s="6"/>
@@ -3548,9 +3400,8 @@
       <c r="L63" s="5"/>
       <c r="M63" s="6"/>
       <c r="N63" s="5"/>
-      <c r="P63" s="6"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="15"/>
       <c r="B64" s="5"/>
       <c r="C64" s="6"/>
@@ -3565,9 +3416,8 @@
       <c r="L64" s="5"/>
       <c r="M64" s="6"/>
       <c r="N64" s="5"/>
-      <c r="P64" s="6"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
@@ -3583,7 +3433,6 @@
       <c r="M65" s="8"/>
       <c r="N65" s="7"/>
       <c r="O65" s="14"/>
-      <c r="P65" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
